--- a/outputs/Vesuvius Way Worksop - Fenster Pricing Document and Review.xlsx
+++ b/outputs/Vesuvius Way Worksop - Fenster Pricing Document and Review.xlsx
@@ -13,7 +13,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quantity Check" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$B$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Pricing Lines'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Pricing Lines'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'TBC &amp; RFIs'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'TBC &amp; RFIs'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Quantity Check'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Quantity Check'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Source Notes'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Source Notes'!$A$1:$B$13</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -476,7 +487,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -500,7 +511,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Staniforth Construction LLP (Joe Mayer)</t>
+          <t>Stainforth Construction LLP (Joe Mayer)</t>
         </is>
       </c>
     </row>
@@ -602,7 +613,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>84922.05</v>
+        <v>85036.77</v>
       </c>
     </row>
     <row r="14">
@@ -632,7 +643,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>110551.98</v>
+        <v>110666.7</v>
       </c>
     </row>
     <row r="17">
@@ -642,7 +653,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>22110.4</v>
+        <v>22133.34</v>
       </c>
     </row>
     <row r="18">
@@ -652,7 +663,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>132662.38</v>
+        <v>132800.04</v>
       </c>
     </row>
     <row r="20">
@@ -709,6 +720,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -716,7 +728,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -905,10 +917,10 @@
         </is>
       </c>
       <c r="I3" s="10" t="n">
-        <v>412.21</v>
+        <v>418.02</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>743.63</v>
+        <v>754.11</v>
       </c>
       <c r="K3" s="10" t="n">
         <v>412.5</v>
@@ -917,7 +929,7 @@
         <v>160</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>1316.13</v>
+        <v>1326.61</v>
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
@@ -1079,10 +1091,10 @@
         </is>
       </c>
       <c r="I6" s="10" t="n">
-        <v>512.5700000000001</v>
+        <v>517.24</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1460.84</v>
+        <v>1474.12</v>
       </c>
       <c r="K6" s="10" t="n">
         <v>1350</v>
@@ -1091,7 +1103,7 @@
         <v>640</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>3450.84</v>
+        <v>3464.12</v>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
@@ -1195,10 +1207,10 @@
         </is>
       </c>
       <c r="I8" s="10" t="n">
-        <v>412.21</v>
+        <v>418.02</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1613.8</v>
+        <v>1636.54</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>825</v>
@@ -1207,7 +1219,7 @@
         <v>320</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>2758.8</v>
+        <v>2781.54</v>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
@@ -1311,10 +1323,10 @@
         </is>
       </c>
       <c r="I10" s="10" t="n">
-        <v>412.21</v>
+        <v>418.02</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>3227.6</v>
+        <v>3273.08</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>1650</v>
@@ -1323,7 +1335,7 @@
         <v>640</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>5517.6</v>
+        <v>5563.08</v>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
@@ -1369,10 +1381,10 @@
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>412.21</v>
+        <v>418.02</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1613.8</v>
+        <v>1636.54</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>825</v>
@@ -1381,7 +1393,7 @@
         <v>320</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>2758.8</v>
+        <v>2781.54</v>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
@@ -1399,7 +1411,7 @@
         <v>112.13</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>84922.05</v>
+        <v>85036.77</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>9262.5</v>
@@ -1408,11 +1420,12 @@
         <v>16367.43</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>110551.98</v>
+        <v>110666.7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1420,7 +1433,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1910,6 +1923,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1917,7 +1931,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1938,7 +1952,7 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>Trade bill (Staniforth)</t>
+          <t>Trade bill (Stainforth)</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
@@ -2220,6 +2234,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2227,7 +2242,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2256,7 +2271,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Trade bill "Aluminium Doors - Windows Bill.xls" (Staniforth, L_SC Aluminium Doors &amp; Windows), cross-read against Logikal drawings 001-008 and JHA drawings 2024-055-221P (door schedule), 222P (window schedule), 127 (door details) and 108D (welfare elevations).</t>
+          <t>Trade bill "Aluminium Doors - Windows Bill.xls" (Stainforth, L_SC Aluminium Doors &amp; Windows), cross-read against Logikal drawings 001-008 and JHA drawings 2024-055-221P (door schedule), 222P (window schedule), 127 (door details) and 108D (welfare elevations).</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2319,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>BSW "aluminium casement window, glazed [&lt;1.5m2]" median GBP 445.71/m2 (542 lines, 87 quotes) + 15% Senior premium = GBP 512.57/m2.</t>
+          <t>BSW "aluminium casement window, glazed [&lt;1.5m2]" median GBP 449.77/m2 (598 lines, 90 quotes) + 15% Senior premium = GBP 517.24/m2.</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2331,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>BSW "aluminium casement window, glazed [1.5-3m2]" median GBP 358.44/m2 (423 lines, 91 quotes) + 15% Senior premium = GBP 412.21/m2.</t>
+          <t>BSW "aluminium casement window, glazed [1.5-3m2]" median GBP 363.50/m2 (446 lines, 96 quotes) + 15% Senior premium = GBP 418.02/m2.</t>
         </is>
       </c>
     </row>
@@ -2394,5 +2409,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/outputs/Vesuvius Way Worksop - Fenster Pricing Document and Review.xlsx
+++ b/outputs/Vesuvius Way Worksop - Fenster Pricing Document and Review.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Quantity Check'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Quantity Check'!$A$1:$F$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Source Notes'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Source Notes'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Source Notes'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2244,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2391,17 +2391,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Mastic, EPDM, structural calculations, SAS curtain wall design, temporary works, scaffold/MEWP, fire-stopping, cladding flashings/pressings (shown as Kingspan/Euroclad scope), roller shutter, internal joinery doors (Howdens), reception screens, and the Building 03 package.</t>
+          <t>Mastic, EPDM, structural calculations, SAS curtain wall design, temporary works, scaffold/MEWP, fire-stopping, CLADDING flashings/pressings (shown as Kingspan/Euroclad scope), roller shutter, internal joinery doors (Howdens), reception screens, and the Building 03 package.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
+          <t>Window flashings - NOT excluded, NOT priced</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Cill, jamb and head flashings to all 13 windows are OURS, not Kingspan/Euroclad. Steve Freezer (Technical Advisor) ruled it 28/07/2026 14:53 and directed the enquiry to Nick at MetFab; Gintare sent it 28/07 16:55 and chased 04/08 08:24 with no return. 63.81 linear metres of pressed aluminium at 13 windows, and this workbook carries GBP 0.00 for it - there is no line to be wrong. Fenster hold NO MetFab rate anywhere (the placed Stoke Park panel order carries a blank cost/m2 and a GBP 0.00 line), so it cannot be benchmarked either. TBC until MetFab return. Until then it is an ALLOWANCE or an EXCLUSION on the issued document - and the exclusion above says "cladding", which does not cover it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>BUDGET. No supplier quote, a specified system Fenster has no live rate for, three quantity conflicts in the tender documents and one item with no drawing. Do not issue as a fixed price.</t>
         </is>
